--- a/data/between_distribution_marketeur.xlsx
+++ b/data/between_distribution_marketeur.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -41,6 +41,27 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Tradex</t>
+  </si>
+  <si>
+    <t>Elf</t>
+  </si>
+  <si>
+    <t>Janvier</t>
+  </si>
+  <si>
+    <t>Juin</t>
+  </si>
+  <si>
+    <t>Mars</t>
+  </si>
+  <si>
+    <t>Avril</t>
   </si>
 </sst>
 </file>
@@ -398,10 +419,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:J1"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="1:10">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -428,6 +449,166 @@
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>950</v>
+      </c>
+      <c r="E2">
+        <v>750</v>
+      </c>
+      <c r="F2">
+        <v>1150</v>
+      </c>
+      <c r="G2">
+        <v>1050</v>
+      </c>
+      <c r="H2">
+        <v>2000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>750</v>
+      </c>
+      <c r="E3">
+        <v>760</v>
+      </c>
+      <c r="F3">
+        <v>550</v>
+      </c>
+      <c r="G3">
+        <v>980</v>
+      </c>
+      <c r="H3">
+        <v>2001</v>
+      </c>
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4">
+        <v>950</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
+        <v>600</v>
+      </c>
+      <c r="G4">
+        <v>450</v>
+      </c>
+      <c r="H4">
+        <v>2002</v>
+      </c>
+      <c r="I4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>650</v>
+      </c>
+      <c r="E5">
+        <v>800</v>
+      </c>
+      <c r="F5">
+        <v>1050</v>
+      </c>
+      <c r="G5">
+        <v>950</v>
+      </c>
+      <c r="H5">
+        <v>2004</v>
+      </c>
+      <c r="I5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>1050</v>
+      </c>
+      <c r="E6">
+        <v>500</v>
+      </c>
+      <c r="F6">
+        <v>980</v>
+      </c>
+      <c r="G6">
+        <v>670</v>
+      </c>
+      <c r="H6">
+        <v>2005</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
